--- a/Impressao 3D/planilha_consignado_chaveiros.xlsx
+++ b/Impressao 3D/planilha_consignado_chaveiros.xlsx
@@ -5,14 +5,14 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
   </bookViews>
   <sheets>
-    <sheet name="Consignado" sheetId="1" r:id="rId1"/>
+    <sheet name="DOUGLAS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -152,13 +152,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,21 +473,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>46123</v>
       </c>
       <c r="C3" t="s">
@@ -507,37 +507,37 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3">
-        <v>3</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
         <v>20</v>
       </c>
     </row>
@@ -545,199 +545,199 @@
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>5</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>6</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="3">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3"/>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="3">
-        <v>3</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
         <v>15</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3">
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
         <v>15</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>7</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="3">
-        <v>3</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3"/>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>8</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>6</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
         <v>15</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="3">
-        <v>3</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3">
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
         <v>15</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>10</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="3">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3">
-        <v>10</v>
-      </c>
-      <c r="G15" s="3"/>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>11</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>6</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3">
-        <v>10</v>
-      </c>
-      <c r="G16" s="3"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2">
+        <v>10</v>
+      </c>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>12</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>5</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3">
-        <v>10</v>
-      </c>
-      <c r="G17" s="3"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>13</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">

--- a/Impressao 3D/planilha_consignado_chaveiros.xlsx
+++ b/Impressao 3D/planilha_consignado_chaveiros.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\REK\Documents\Estudos Claudio\impressao-3D\Impressao 3D\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\Estudos\impressao-3D\Impressao 3D\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>CONEXÃO 3D CRIATIVA – CONTROLE DE CONSIGNADO DE CHAVEIROS</t>
   </si>
@@ -115,6 +115,15 @@
   </si>
   <si>
     <t>Chaveiro A-KA 47</t>
+  </si>
+  <si>
+    <t>Chaveiro taça</t>
+  </si>
+  <si>
+    <t>Chaveiro Bandeira</t>
+  </si>
+  <si>
+    <t>Chaveiro CBF</t>
   </si>
 </sst>
 </file>
@@ -150,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -158,6 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -461,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.28515625" customWidth="1"/>
@@ -473,15 +483,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -538,7 +548,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -554,7 +564,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7" s="2"/>
     </row>
@@ -571,7 +581,7 @@
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -588,7 +598,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -605,7 +615,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G10" s="2"/>
     </row>
@@ -622,7 +632,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -639,7 +649,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G12" s="2"/>
     </row>
@@ -656,7 +666,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -673,7 +683,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G14" s="2"/>
     </row>
@@ -690,7 +700,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -707,7 +717,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G16" s="2"/>
     </row>
@@ -724,53 +734,93 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>13</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2">
+        <v>5</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="F18" s="2">
+        <v>8</v>
+      </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>13</v>
-      </c>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>18</v>
       </c>
     </row>
